--- a/artfynd/A 61894-2024 artfynd.xlsx
+++ b/artfynd/A 61894-2024 artfynd.xlsx
@@ -789,7 +789,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121712704</v>
+        <v>121713463</v>
       </c>
       <c r="B3" t="n">
         <v>57373</v>
@@ -829,13 +829,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552448</v>
+        <v>552486</v>
       </c>
       <c r="R3" t="n">
-        <v>6276363</v>
+        <v>6276504</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,6 +865,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-12-22</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,7 +896,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121713463</v>
+        <v>121712704</v>
       </c>
       <c r="B4" t="n">
         <v>57373</v>
@@ -931,13 +936,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552486</v>
+        <v>552448</v>
       </c>
       <c r="R4" t="n">
-        <v>6276504</v>
+        <v>6276363</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -967,11 +972,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-12-22</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 61894-2024 artfynd.xlsx
+++ b/artfynd/A 61894-2024 artfynd.xlsx
@@ -789,7 +789,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121713463</v>
+        <v>121712704</v>
       </c>
       <c r="B3" t="n">
         <v>57373</v>
@@ -829,13 +829,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552486</v>
+        <v>552448</v>
       </c>
       <c r="R3" t="n">
-        <v>6276504</v>
+        <v>6276363</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,11 +865,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-12-22</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,7 +891,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121712704</v>
+        <v>121713463</v>
       </c>
       <c r="B4" t="n">
         <v>57373</v>
@@ -936,13 +931,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552448</v>
+        <v>552486</v>
       </c>
       <c r="R4" t="n">
-        <v>6276363</v>
+        <v>6276504</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -972,6 +967,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-12-22</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 61894-2024 artfynd.xlsx
+++ b/artfynd/A 61894-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>87424696</v>
       </c>
       <c r="B2" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -717,10 +712,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>552482.8953806136</v>
+        <v>552483</v>
       </c>
       <c r="R2" t="n">
-        <v>6276495.309072563</v>
+        <v>6276495</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -792,16 +787,11 @@
         <v>121712704</v>
       </c>
       <c r="B3" t="n">
-        <v>57385</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -894,16 +884,11 @@
         <v>121713463</v>
       </c>
       <c r="B4" t="n">
-        <v>57385</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -995,6 +980,119 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>66449787</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Alsjöholmsvägen, Alsjösjön, Nybro, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>552469</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6276306</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Oskar</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2017-06-28</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2017-06-28</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Eric Lundén</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Eric Lundén</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61894-2024 artfynd.xlsx
+++ b/artfynd/A 61894-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87424696</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -878,6 +888,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121712704</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -980,6 +995,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121713463</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1093,8 +1113,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66449787</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>